--- a/gex_pivot_levels_2026-09-08.xlsx
+++ b/gex_pivot_levels_2026-09-08.xlsx
@@ -15,12 +15,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Pivots" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ES'!$A$1:$G$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ES'!$A$1:$G$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'NQ'!$A$1:$G$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RTY'!$A$1:$G$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CL'!$A$1:$G$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'GC'!$A$1:$G$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'All Pivots'!$A$1:$H$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'All Pivots'!$A$1:$H$80</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -91,6 +91,15 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -98,15 +107,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -532,10 +532,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>7653.4</v>
+        <v>7603.4</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>7650</v>
+        <v>7600</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
@@ -544,440 +544,498 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>-$19.05M</t>
+          <t>-$3.79M</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>+$24.37M</t>
+          <t>+$6.17M</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
-        <v>7668.4</v>
-      </c>
-      <c r="B3" s="5" t="n">
-        <v>7665</v>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="A3" s="2" t="n">
+        <v>7633.4</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>7630</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>-$4.77M</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>+$6.94M</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>-$7.92M</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>+$9.13M</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
+        <v>7653.4</v>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>7650</v>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>-$22.71M</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>+$29.06M</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>7668.4</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>7665</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>-$5.37M</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>+$7.82M</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
         <v>7669.99</v>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B6" s="2" t="n">
         <v>765</v>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>-$20.30M</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>+$34.29M</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="G6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
         <v>7673.4</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B7" s="2" t="n">
         <v>7670</v>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>-$14.15M</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>+$19.87M</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>-$15.60M</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>+$21.91M</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="n">
-        <v>7683.4</v>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>7680</v>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7678.4</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>7675</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>-$12.89M</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>+$24.44M</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>-$12.65M</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>+$25.96M</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="n">
-        <v>7698.4</v>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>7695</v>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>+$10.88M</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>+$23.64M</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="n">
-        <v>7700.05</v>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>768</v>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>-$24.87M</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>+$45.00M</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+      <c r="G8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>7703.4</v>
+        <v>7698.4</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>7700</v>
+        <v>7695</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>-$12.47M</t>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>+$10.45M</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>+$56.00M</t>
+          <t>+$22.70M</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Net</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>7700.05</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>768</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>-$24.87M</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>+$45.00M</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
           <t>valley</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="n">
-        <v>7720.1</v>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>770</v>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>-$543.65K</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>+$114.66M</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>7728.4</v>
+        <v>7703.4</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>7725</v>
+        <v>7700</v>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>+$2.64M</t>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>-$11.60M</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>+$21.03M</t>
+          <t>+$52.12M</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>7718.4</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>7715</v>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>+$158.54K</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>+$17.83M</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="n">
-        <v>7750.16</v>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>773</v>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>+$26.30M</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>+$59.38M</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+      <c r="G12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
+        <v>7720.1</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>770</v>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>-$543.65K</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>+$114.66M</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>7750.16</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>773</v>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>+$26.30M</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>+$59.38M</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
         <v>7753.4</v>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B15" s="5" t="n">
         <v>7750</v>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>+$8.99M</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>+$22.10M</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>+$7.01M</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>+$17.25M</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="n">
+    <row r="16">
+      <c r="A16" s="2" t="n">
         <v>7760.18</v>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B16" s="2" t="n">
         <v>774</v>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>+$15.37M</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>+$26.63M</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
+    <row r="17">
+      <c r="A17" s="5" t="n">
         <v>7770.2</v>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B17" s="5" t="n">
         <v>775</v>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>+$41.26M</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>+$46.94M</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G15"/>
+  <autoFilter ref="A1:G17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1039,112 +1097,112 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="5" t="n">
         <v>29197.06</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="5" t="n">
         <v>710</v>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>-$20.92M</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>+$23.43M</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="2" t="n">
         <v>29238.15</v>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="2" t="n">
         <v>711</v>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>-$3.39M</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>+$5.54M</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="5" t="n">
         <v>29361.43</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="5" t="n">
         <v>714</v>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>-$32.58M</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>+$40.60M</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="2" t="n">
         <v>29381.1</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="2" t="n">
         <v>29360</v>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
@@ -1154,26 +1212,26 @@
           <t>+$67.36K</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>+$88.63K</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="2" t="n">
         <v>29391.1</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="2" t="n">
         <v>29370</v>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
@@ -1183,92 +1241,92 @@
           <t>+$78.00K</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>+$78.00K</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="2" t="n">
         <v>29401.1</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="2" t="n">
         <v>29380</v>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>-$30.73K</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>+$168.99K</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="5" t="n">
         <v>29421.1</v>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="5" t="n">
         <v>29400</v>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>-$92.18K</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>+$345.67K</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="5" t="n">
         <v>29446.1</v>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B9" s="5" t="n">
         <v>29425</v>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
@@ -1278,63 +1336,63 @@
           <t>+$78.59K</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>+$95.13K</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="5" t="n">
         <v>29461.1</v>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" s="5" t="n">
         <v>29440</v>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>-$78.59K</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>+$235.76K</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="5" t="n">
         <v>29511.1</v>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B11" s="5" t="n">
         <v>29490</v>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
@@ -1344,92 +1402,92 @@
           <t>+$553.95K</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>+$580.54K</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="2" t="n">
         <v>29525.8</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="2" t="n">
         <v>718</v>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>-$3.20M</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>+$41.56M</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr"/>
+      <c r="G12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="5" t="n">
         <v>29541.1</v>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B13" s="5" t="n">
         <v>29520</v>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>-$13.29K</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>+$208.29K</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="2" t="n">
         <v>29571.1</v>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="2" t="n">
         <v>29550</v>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
@@ -1439,26 +1497,26 @@
           <t>+$137.38K</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>+$332.37K</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="5" t="n">
         <v>29591.1</v>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B15" s="5" t="n">
         <v>29570</v>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
@@ -1468,63 +1526,63 @@
           <t>+$155.11K</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>+$181.70K</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="2" t="n">
         <v>29596.1</v>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="2" t="n">
         <v>29575</v>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>-$17.73K</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>+$141.81K</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="5" t="n">
         <v>29607.99</v>
       </c>
-      <c r="B17" s="2" t="n">
+      <c r="B17" s="5" t="n">
         <v>720</v>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
@@ -1534,30 +1592,30 @@
           <t>+$17.61M</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>+$63.09M</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="2" t="n">
         <v>29611.1</v>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B18" s="2" t="n">
         <v>29590</v>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
@@ -1567,30 +1625,30 @@
           <t>+$97.50K</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>+$106.36K</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="2" t="n">
         <v>29621.1</v>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="2" t="n">
         <v>29600</v>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
@@ -1600,26 +1658,26 @@
           <t>+$66.47K</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>+$190.56K</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="2" t="n">
         <v>29649.08</v>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B20" s="2" t="n">
         <v>721</v>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
@@ -1629,30 +1687,30 @@
           <t>+$7.64M</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>+$27.35M</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="2" t="n">
         <v>29651.1</v>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B21" s="2" t="n">
         <v>29630</v>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
@@ -1662,59 +1720,59 @@
           <t>+$57.91K</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>+$124.09K</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="5" t="n">
         <v>29671.1</v>
       </c>
-      <c r="B22" s="2" t="n">
+      <c r="B22" s="5" t="n">
         <v>29650</v>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>-$62.04K</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>+$177.86K</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="2" t="n">
         <v>29690.17</v>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="B23" s="2" t="n">
         <v>722</v>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
@@ -1724,30 +1782,30 @@
           <t>+$18.32M</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>+$26.79M</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="2" t="n">
         <v>29721.1</v>
       </c>
-      <c r="B24" s="5" t="n">
+      <c r="B24" s="2" t="n">
         <v>29700</v>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
@@ -1757,26 +1815,26 @@
           <t>+$46.09K</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>+$67.36K</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="2" t="n">
         <v>29813.45</v>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B25" s="2" t="n">
         <v>725</v>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
@@ -1786,17 +1844,17 @@
           <t>+$14.40M</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>+$17.26M</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G25"/>
@@ -1861,46 +1919,46 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="5" t="n">
         <v>2957.64</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="5" t="n">
         <v>294</v>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>-$23.58M</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>+$29.67M</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="5" t="n">
         <v>2987.82</v>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="5" t="n">
         <v>297</v>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
@@ -1910,30 +1968,30 @@
           <t>+$59.06M</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>+$65.44M</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="2" t="n">
         <v>3018</v>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
@@ -1943,17 +2001,17 @@
           <t>+$11.02M</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>+$11.44M</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G4"/>
@@ -2018,178 +2076,178 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="5" t="n">
         <v>83.77</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="5" t="n">
         <v>130</v>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>-$1.26M</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>+$1.32M</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="2" t="n">
         <v>84.42</v>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="2" t="n">
         <v>131</v>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>-$18.65K</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>+$34.94K</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="5" t="n">
         <v>85.06</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="5" t="n">
         <v>132</v>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>-$621.67K</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>+$633.10K</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="2" t="n">
         <v>85.70999999999999</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="2" t="n">
         <v>133</v>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>-$82.62K</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>+$187.73K</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="5" t="n">
         <v>86.98999999999999</v>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="5" t="n">
         <v>135</v>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>-$929.66K</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>+$1.26M</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="2" t="n">
         <v>88.93000000000001</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="2" t="n">
         <v>138</v>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
@@ -2199,55 +2257,55 @@
           <t>+$372.14K</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>+$923.08K</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="2" t="n">
         <v>90.22</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="2" t="n">
         <v>140</v>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>-$9.56K</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>+$1.34M</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="2" t="n">
         <v>91.51000000000001</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="2" t="n">
         <v>142</v>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
@@ -2257,26 +2315,26 @@
           <t>+$480.51K</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>+$1.02M</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="5" t="n">
         <v>93.44</v>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" s="5" t="n">
         <v>145</v>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
@@ -2286,30 +2344,30 @@
           <t>+$1.67M</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>+$1.75M</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="2" t="n">
         <v>94.08</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="2" t="n">
         <v>146</v>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
@@ -2319,30 +2377,30 @@
           <t>+$55.63K</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>+$113.65K</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="2" t="n">
         <v>95.37</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="2" t="n">
         <v>148</v>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
@@ -2352,26 +2410,26 @@
           <t>+$300.46K</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>+$302.82K</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr"/>
+      <c r="G12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="5" t="n">
         <v>96.66</v>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B13" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
@@ -2381,30 +2439,30 @@
           <t>+$1.81M</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>+$1.81M</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="2" t="n">
         <v>99.23999999999999</v>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="2" t="n">
         <v>154</v>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
@@ -2414,30 +2472,30 @@
           <t>+$3.06K</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>+$3.06K</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="5" t="n">
         <v>99.88</v>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B15" s="5" t="n">
         <v>155</v>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
@@ -2447,30 +2505,30 @@
           <t>+$536.61K</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>+$536.61K</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="2" t="n">
         <v>101.17</v>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="2" t="n">
         <v>157</v>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
@@ -2480,30 +2538,30 @@
           <t>+$3.55K</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>+$3.55K</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="5" t="n">
         <v>101.49</v>
       </c>
-      <c r="B17" s="2" t="n">
+      <c r="B17" s="5" t="n">
         <v>157.5</v>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
@@ -2513,30 +2571,30 @@
           <t>+$654.98K</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>+$654.98K</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="2" t="n">
         <v>102.46</v>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B18" s="2" t="n">
         <v>159</v>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
@@ -2546,17 +2604,17 @@
           <t>+$307</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>+$307</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
@@ -2625,71 +2683,71 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="2" t="n">
         <v>4058.98</v>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B2" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>-$1.60M</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>+$1.71M</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="2" t="n">
         <v>4149.18</v>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="2" t="n">
         <v>92</v>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>-$2.06M</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>+$2.18M</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="2" t="n">
         <v>4194.28</v>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="2" t="n">
         <v>93</v>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
@@ -2699,257 +2757,257 @@
           <t>+$93.38K</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>+$433.51K</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="5" t="n">
         <v>4284.48</v>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="5" t="n">
         <v>95</v>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>-$3.07M</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>+$3.68M</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="2" t="n">
         <v>4380.08</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="2" t="n">
         <v>398</v>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>-$683.99K</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>+$805.25K</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="5" t="n">
         <v>4402.09</v>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="5" t="n">
         <v>400</v>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>-$1.91M</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>+$2.67M</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="2" t="n">
         <v>4413.1</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="2" t="n">
         <v>401</v>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>-$207.99K</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>+$438.12K</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="5" t="n">
         <v>4424.11</v>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B9" s="5" t="n">
         <v>402</v>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>-$1.87M</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>+$2.12M</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="2" t="n">
         <v>4435.11</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="2" t="n">
         <v>403</v>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>-$712.73K</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>+$958.97K</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="5" t="n">
         <v>4446.12</v>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B11" s="5" t="n">
         <v>404</v>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>-$5.05M</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>+$5.79M</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="2" t="n">
         <v>4464.87</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="2" t="n">
         <v>99</v>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
@@ -2959,26 +3017,26 @@
           <t>+$3.50M</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>+$6.72M</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr"/>
+      <c r="G12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="5" t="n">
         <v>4512.15</v>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B13" s="5" t="n">
         <v>410</v>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
@@ -2988,30 +3046,30 @@
           <t>+$1.73M</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>+$3.70M</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="5" t="n">
         <v>4555.07</v>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B14" s="5" t="n">
         <v>101</v>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
@@ -3021,30 +3079,30 @@
           <t>+$10.98M</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>+$11.25M</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="2" t="n">
         <v>4556.17</v>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="2" t="n">
         <v>414</v>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
@@ -3054,30 +3112,30 @@
           <t>+$255.45K</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>+$657.15K</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="5" t="n">
         <v>4578.18</v>
       </c>
-      <c r="B16" s="2" t="n">
+      <c r="B16" s="5" t="n">
         <v>416</v>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
@@ -3087,30 +3145,30 @@
           <t>+$1.76M</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>+$1.82M</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="2" t="n">
         <v>4645.27</v>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="2" t="n">
         <v>103</v>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
@@ -3120,30 +3178,30 @@
           <t>+$3.36M</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>+$3.57M</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="5" t="n">
         <v>4690.37</v>
       </c>
-      <c r="B18" s="2" t="n">
+      <c r="B18" s="5" t="n">
         <v>104</v>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
@@ -3153,30 +3211,30 @@
           <t>+$8.86M</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>+$8.95M</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="2" t="n">
         <v>4735.47</v>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="2" t="n">
         <v>105</v>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
@@ -3186,30 +3244,30 @@
           <t>+$2.16M</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>+$2.25M</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="5" t="n">
         <v>4780.57</v>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="B20" s="5" t="n">
         <v>106</v>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
@@ -3219,17 +3277,17 @@
           <t>+$4.47M</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>+$4.48M</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -3248,7 +3306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3304,52 +3362,52 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B2" s="2" t="n">
         <v>7720.1</v>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="2" t="n">
         <v>770</v>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>-$543.65K</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>+$114.66M</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>RTY</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="5" t="n">
         <v>2987.82</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="5" t="n">
         <v>297</v>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
@@ -3359,35 +3417,35 @@
           <t>+$59.06M</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>+$65.44M</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="5" t="n">
         <v>29607.99</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="5" t="n">
         <v>720</v>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
@@ -3397,35 +3455,35 @@
           <t>+$17.61M</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>+$63.09M</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="2" t="n">
         <v>7750.16</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="2" t="n">
         <v>773</v>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
@@ -3435,73 +3493,73 @@
           <t>+$26.30M</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>+$59.38M</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="5" t="n">
         <v>7703.4</v>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="5" t="n">
         <v>7700</v>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>-$12.47M</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>+$56.00M</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>-$11.60M</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>+$52.12M</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="5" t="n">
         <v>7770.2</v>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="5" t="n">
         <v>775</v>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
@@ -3511,199 +3569,199 @@
           <t>+$41.26M</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>+$46.94M</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="2" t="n">
         <v>7700.05</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="2" t="n">
         <v>768</v>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>-$24.87M</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>+$45.00M</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="2" t="n">
         <v>29525.8</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="2" t="n">
         <v>718</v>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>-$3.20M</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>+$41.56M</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" s="5" t="n">
         <v>29361.43</v>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C10" s="5" t="n">
         <v>714</v>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>-$32.58M</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>+$40.60M</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="2" t="n">
         <v>7669.99</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="2" t="n">
         <v>765</v>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>-$20.30M</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>+$34.29M</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>RTY</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B12" s="5" t="n">
         <v>2957.64</v>
       </c>
-      <c r="C12" s="2" t="n">
+      <c r="C12" s="5" t="n">
         <v>294</v>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>-$23.58M</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>+$29.67M</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
@@ -3712,150 +3770,154 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>7653.4</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>7650</v>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>-$22.71M</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>+$29.06M</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B14" s="2" t="n">
         <v>29649.08</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C14" s="2" t="n">
         <v>721</v>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>+$7.64M</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>+$27.35M</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B15" s="2" t="n">
         <v>29690.17</v>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C15" s="2" t="n">
         <v>722</v>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>+$18.32M</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>+$26.79M</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B16" s="2" t="n">
         <v>7760.18</v>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C16" s="2" t="n">
         <v>774</v>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>+$15.37M</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>+$26.63M</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n">
-        <v>7683.4</v>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>7680</v>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>-$12.89M</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>+$24.44M</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -3864,10 +3926,10 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>7653.4</v>
+        <v>7678.4</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>7650</v>
+        <v>7675</v>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
@@ -3876,98 +3938,94 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>-$19.05M</t>
+          <t>-$12.65M</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>+$24.37M</t>
+          <t>+$25.96M</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>7698.4</v>
+        <v>29197.06</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>7695</v>
+        <v>710</v>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>+$10.88M</t>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>-$20.92M</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>+$23.64M</t>
+          <t>+$23.43M</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>29197.06</v>
+        <v>7698.4</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>710</v>
+        <v>7695</v>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>-$20.92M</t>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>+$10.45M</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>+$23.43M</t>
+          <t>+$22.70M</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Net</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
@@ -3978,190 +4036,190 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>7753.4</v>
+        <v>7673.4</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>7750</v>
+        <v>7670</v>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>+$8.99M</t>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>-$15.60M</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>+$22.10M</t>
+          <t>+$21.91M</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Net</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n">
-        <v>7728.4</v>
-      </c>
-      <c r="C21" s="5" t="n">
-        <v>7725</v>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="B21" s="2" t="n">
+        <v>7718.4</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>7715</v>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>+$2.64M</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>+$21.03M</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
+          <t>+$158.54K</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>+$17.83M</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>7673.4</v>
-      </c>
-      <c r="C22" s="5" t="n">
-        <v>7670</v>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>-$14.15M</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>+$19.87M</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>29813.45</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>725</v>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>+$14.40M</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>+$17.26M</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>29813.45</v>
+        <v>7753.4</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>725</v>
+        <v>7750</v>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>+$14.40M</t>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>+$7.01M</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>+$17.26M</t>
+          <t>+$17.25M</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>RTY</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>3018</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>+$11.02M</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>+$11.44M</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>RTY</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>3018</v>
-      </c>
-      <c r="C24" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>IWM</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>+$11.02M</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>+$11.44M</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="B25" s="2" t="n">
+      <c r="B25" s="5" t="n">
         <v>4555.07</v>
       </c>
-      <c r="C25" s="2" t="n">
+      <c r="C25" s="5" t="n">
         <v>101</v>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
@@ -4171,17 +4229,17 @@
           <t>+$10.98M</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <t>+$11.25M</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -4190,112 +4248,112 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>4690.37</v>
+        <v>7633.4</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>104</v>
+        <v>7630</v>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>+$8.86M</t>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>-$7.92M</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>+$8.95M</t>
+          <t>+$9.13M</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>4690.37</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>104</v>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>+$8.86M</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>+$8.95M</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B28" s="2" t="n">
         <v>7668.4</v>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C28" s="2" t="n">
         <v>7665</v>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>-$4.77M</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>+$6.94M</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>-$5.37M</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>+$7.82M</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="n">
-        <v>4464.87</v>
-      </c>
-      <c r="C28" s="5" t="n">
-        <v>99</v>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>+$3.50M</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>+$6.72M</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -4304,186 +4362,178 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
+        <v>4464.87</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>+$3.50M</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>+$6.72M</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>7603.4</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>7600</v>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>-$3.79M</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>+$6.17M</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
         <v>4446.12</v>
       </c>
-      <c r="C29" s="2" t="n">
+      <c r="C31" s="5" t="n">
         <v>404</v>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>-$5.05M</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <t>+$5.79M</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
         <is>
           <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="n">
-        <v>29238.15</v>
-      </c>
-      <c r="C30" s="5" t="n">
-        <v>711</v>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>-$3.39M</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>+$5.54M</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>4780.57</v>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>106</v>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>+$4.47M</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>+$4.48M</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>29238.15</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>711</v>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>-$3.39M</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>+$5.54M</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="B32" s="2" t="n">
-        <v>4512.15</v>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>410</v>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t>+$1.73M</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>+$3.70M</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="B33" s="5" t="n">
+        <v>4780.57</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>+$4.47M</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>+$4.48M</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
         <is>
           <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>4284.48</v>
-      </c>
-      <c r="C33" s="2" t="n">
-        <v>95</v>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>-$3.07M</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>+$3.68M</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
         </is>
       </c>
     </row>
@@ -4494,108 +4544,108 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
+        <v>4512.15</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>410</v>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>+$1.73M</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>+$3.70M</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>4284.48</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>-$3.07M</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>+$3.68M</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
         <v>4645.27</v>
       </c>
-      <c r="C34" s="5" t="n">
+      <c r="C36" s="2" t="n">
         <v>103</v>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr">
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t>+$3.36M</t>
         </is>
       </c>
-      <c r="F34" s="6" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t>+$3.57M</t>
         </is>
       </c>
-      <c r="G34" s="6" t="inlineStr">
+      <c r="G36" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H34" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>4402.09</v>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>400</v>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>-$1.91M</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>+$2.67M</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="n">
-        <v>4735.47</v>
-      </c>
-      <c r="C36" s="5" t="n">
-        <v>105</v>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t>+$2.16M</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="inlineStr">
-        <is>
-          <t>+$2.25M</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H36" s="6" t="inlineStr">
+      <c r="H36" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
@@ -4608,32 +4658,36 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>4149.18</v>
+        <v>4402.09</v>
       </c>
       <c r="C37" s="5" t="n">
-        <v>92</v>
+        <v>400</v>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>GLD</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>-$2.06M</t>
+          <t>-$1.91M</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>+$2.18M</t>
+          <t>+$2.67M</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H37" s="6" t="inlineStr"/>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -4642,29 +4696,29 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>4424.11</v>
+        <v>4735.47</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>402</v>
+        <v>105</v>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>-$1.87M</t>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>+$2.16M</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>+$2.12M</t>
+          <t>+$2.25M</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Net</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
@@ -4680,108 +4734,104 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
+        <v>4149.18</v>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>-$2.06M</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>+$2.18M</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>4424.11</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>402</v>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>-$1.87M</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>+$2.12M</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
         <v>4578.18</v>
       </c>
-      <c r="C39" s="2" t="n">
+      <c r="C41" s="5" t="n">
         <v>416</v>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="E39" s="9" t="inlineStr">
+      <c r="E41" s="9" t="inlineStr">
         <is>
           <t>+$1.76M</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <t>+$1.82M</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>96.66</v>
-      </c>
-      <c r="C40" s="2" t="n">
-        <v>150</v>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E40" s="9" t="inlineStr">
-        <is>
-          <t>+$1.81M</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>+$1.81M</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n">
-        <v>93.44</v>
-      </c>
-      <c r="C41" s="2" t="n">
-        <v>145</v>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E41" s="9" t="inlineStr">
-        <is>
-          <t>+$1.67M</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>+$1.75M</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -4790,36 +4840,40 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>4058.98</v>
+        <v>96.66</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>-$1.60M</t>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>+$1.81M</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>+$1.71M</t>
+          <t>+$1.81M</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H42" s="6" t="inlineStr"/>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -4828,70 +4882,70 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>90.22</v>
+        <v>93.44</v>
       </c>
       <c r="C43" s="5" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>-$9.56K</t>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>+$1.67M</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>+$1.34M</t>
+          <t>+$1.75M</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H43" s="6" t="inlineStr"/>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>83.77</v>
+        <v>4058.98</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>USO</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>-$1.26M</t>
+          <t>-$1.60M</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>+$1.32M</t>
+          <t>+$1.71M</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -4900,10 +4954,10 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>86.98999999999999</v>
+        <v>90.22</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
@@ -4912,24 +4966,20 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>-$929.66K</t>
+          <t>-$9.56K</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>+$1.26M</t>
+          <t>+$1.34M</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -4938,359 +4988,359 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>91.51000000000001</v>
+        <v>83.77</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="E46" s="8" t="inlineStr">
-        <is>
-          <t>+$480.51K</t>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>-$1.26M</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>+$1.02M</t>
+          <t>+$1.32M</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H46" s="6" t="inlineStr"/>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>86.98999999999999</v>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>-$929.66K</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>+$1.26M</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>91.51000000000001</v>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>+$480.51K</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>+$1.02M</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="B47" s="5" t="n">
+      <c r="B49" s="2" t="n">
         <v>4435.11</v>
       </c>
-      <c r="C47" s="5" t="n">
+      <c r="C49" s="2" t="n">
         <v>403</v>
       </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr">
+      <c r="E49" s="4" t="inlineStr">
         <is>
           <t>-$712.73K</t>
         </is>
       </c>
-      <c r="F47" s="6" t="inlineStr">
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>+$958.97K</t>
         </is>
       </c>
-      <c r="G47" s="6" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H47" s="6" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="B48" s="5" t="n">
+      <c r="B50" s="2" t="n">
         <v>88.93000000000001</v>
       </c>
-      <c r="C48" s="5" t="n">
+      <c r="C50" s="2" t="n">
         <v>138</v>
       </c>
-      <c r="D48" s="6" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="E48" s="8" t="inlineStr">
+      <c r="E50" s="8" t="inlineStr">
         <is>
           <t>+$372.14K</t>
         </is>
       </c>
-      <c r="F48" s="6" t="inlineStr">
+      <c r="F50" s="3" t="inlineStr">
         <is>
           <t>+$923.08K</t>
         </is>
       </c>
-      <c r="G48" s="6" t="inlineStr">
+      <c r="G50" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H48" s="6" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="n">
-        <v>4380.08</v>
-      </c>
-      <c r="C49" s="5" t="n">
-        <v>398</v>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>-$683.99K</t>
-        </is>
-      </c>
-      <c r="F49" s="6" t="inlineStr">
-        <is>
-          <t>+$805.25K</t>
-        </is>
-      </c>
-      <c r="G49" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H49" s="6" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="n">
-        <v>4556.17</v>
-      </c>
-      <c r="C50" s="5" t="n">
-        <v>414</v>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E50" s="8" t="inlineStr">
-        <is>
-          <t>+$255.45K</t>
-        </is>
-      </c>
-      <c r="F50" s="6" t="inlineStr">
-        <is>
-          <t>+$657.15K</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H50" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+      <c r="H50" s="3" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>101.49</v>
+        <v>4380.08</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>157.5</v>
+        <v>398</v>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E51" s="9" t="inlineStr">
-        <is>
-          <t>+$654.98K</t>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>-$683.99K</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>+$654.98K</t>
+          <t>+$805.25K</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>4556.17</v>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>414</v>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>+$255.45K</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>+$657.15K</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="B52" s="2" t="n">
+      <c r="B53" s="5" t="n">
+        <v>101.49</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>157.5</v>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t>+$654.98K</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>+$654.98K</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
         <v>85.06</v>
       </c>
-      <c r="C52" s="2" t="n">
+      <c r="C54" s="5" t="n">
         <v>132</v>
       </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="D54" s="6" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
+      <c r="E54" s="7" t="inlineStr">
         <is>
           <t>-$621.67K</t>
         </is>
       </c>
-      <c r="F52" s="3" t="inlineStr">
+      <c r="F54" s="6" t="inlineStr">
         <is>
           <t>+$633.10K</t>
         </is>
       </c>
-      <c r="G52" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
         <is>
           <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="n">
-        <v>29511.1</v>
-      </c>
-      <c r="C53" s="2" t="n">
-        <v>29490</v>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E53" s="9" t="inlineStr">
-        <is>
-          <t>+$553.95K</t>
-        </is>
-      </c>
-      <c r="F53" s="3" t="inlineStr">
-        <is>
-          <t>+$580.54K</t>
-        </is>
-      </c>
-      <c r="G53" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="n">
-        <v>99.88</v>
-      </c>
-      <c r="C54" s="2" t="n">
-        <v>155</v>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E54" s="9" t="inlineStr">
-        <is>
-          <t>+$536.61K</t>
-        </is>
-      </c>
-      <c r="F54" s="3" t="inlineStr">
-        <is>
-          <t>+$536.61K</t>
-        </is>
-      </c>
-      <c r="G54" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>4413.1</v>
+        <v>29511.1</v>
       </c>
       <c r="C55" s="5" t="n">
-        <v>401</v>
+        <v>29490</v>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>-$207.99K</t>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t>+$553.95K</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>+$438.12K</t>
+          <t>+$580.54K</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H55" s="6" t="inlineStr">
@@ -5302,33 +5352,33 @@
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B56" s="5" t="n">
-        <v>4194.28</v>
+        <v>99.88</v>
       </c>
       <c r="C56" s="5" t="n">
-        <v>93</v>
+        <v>155</v>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E56" s="8" t="inlineStr">
-        <is>
-          <t>+$93.38K</t>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E56" s="9" t="inlineStr">
+        <is>
+          <t>+$536.61K</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>+$433.51K</t>
+          <t>+$536.61K</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H56" s="6" t="inlineStr">
@@ -5340,108 +5390,116 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>29421.1</v>
+        <v>4413.1</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>29400</v>
+        <v>401</v>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>NDX</t>
+          <t>GLD</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>-$92.18K</t>
+          <t>-$207.99K</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>+$345.67K</t>
+          <t>+$438.12K</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Net</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="n">
-        <v>29571.1</v>
-      </c>
-      <c r="C58" s="5" t="n">
-        <v>29550</v>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>4194.28</v>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>GDX</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>+$137.38K</t>
-        </is>
-      </c>
-      <c r="F58" s="6" t="inlineStr">
-        <is>
-          <t>+$332.37K</t>
-        </is>
-      </c>
-      <c r="G58" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H58" s="6" t="inlineStr"/>
+          <t>+$93.38K</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>+$433.51K</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B59" s="5" t="n">
-        <v>95.37</v>
+        <v>29421.1</v>
       </c>
       <c r="C59" s="5" t="n">
-        <v>148</v>
+        <v>29400</v>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E59" s="8" t="inlineStr">
-        <is>
-          <t>+$300.46K</t>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>-$92.18K</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>+$302.82K</t>
+          <t>+$345.67K</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H59" s="6" t="inlineStr"/>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -5450,74 +5508,66 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>29461.1</v>
+        <v>29571.1</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>29440</v>
+        <v>29550</v>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>-$78.59K</t>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>+$137.38K</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>+$235.76K</t>
+          <t>+$332.37K</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>29541.1</v>
+        <v>95.37</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>29520</v>
+        <v>148</v>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>-$13.29K</t>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>+$300.46K</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>+$208.29K</t>
+          <t>+$302.82K</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
@@ -5526,68 +5576,72 @@
         </is>
       </c>
       <c r="B62" s="5" t="n">
-        <v>29621.1</v>
+        <v>29461.1</v>
       </c>
       <c r="C62" s="5" t="n">
-        <v>29600</v>
+        <v>29440</v>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E62" s="8" t="inlineStr">
-        <is>
-          <t>+$66.47K</t>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>-$78.59K</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>+$190.56K</t>
+          <t>+$235.76K</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H62" s="6" t="inlineStr"/>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B63" s="5" t="n">
-        <v>85.70999999999999</v>
+        <v>29541.1</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>133</v>
+        <v>29520</v>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>USO</t>
+          <t>NDX</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>-$82.62K</t>
+          <t>-$13.29K</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>+$187.73K</t>
+          <t>+$208.29K</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
@@ -5598,72 +5652,68 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>29591.1</v>
+        <v>29621.1</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>29570</v>
+        <v>29600</v>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E64" s="9" t="inlineStr">
-        <is>
-          <t>+$155.11K</t>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>+$66.47K</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>+$181.70K</t>
+          <t>+$190.56K</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>29671.1</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>29650</v>
+        <v>133</v>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>NDX</t>
+          <t>USO</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>-$62.04K</t>
+          <t>-$82.62K</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>+$177.86K</t>
+          <t>+$187.73K</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Net</t>
         </is>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
@@ -5674,32 +5724,36 @@
         </is>
       </c>
       <c r="B66" s="5" t="n">
-        <v>29401.1</v>
+        <v>29591.1</v>
       </c>
       <c r="C66" s="5" t="n">
-        <v>29380</v>
+        <v>29570</v>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E66" s="7" t="inlineStr">
-        <is>
-          <t>-$30.73K</t>
+      <c r="E66" s="9" t="inlineStr">
+        <is>
+          <t>+$155.11K</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>+$168.99K</t>
+          <t>+$181.70K</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H66" s="6" t="inlineStr"/>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
@@ -5708,218 +5762,218 @@
         </is>
       </c>
       <c r="B67" s="5" t="n">
+        <v>29671.1</v>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>29650</v>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>-$62.04K</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>+$177.86K</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>29401.1</v>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>29380</v>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>-$30.73K</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>+$168.99K</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n">
         <v>29596.1</v>
       </c>
-      <c r="C67" s="5" t="n">
+      <c r="C69" s="2" t="n">
         <v>29575</v>
       </c>
-      <c r="D67" s="6" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E67" s="7" t="inlineStr">
+      <c r="E69" s="4" t="inlineStr">
         <is>
           <t>-$17.73K</t>
         </is>
       </c>
-      <c r="F67" s="6" t="inlineStr">
+      <c r="F69" s="3" t="inlineStr">
         <is>
           <t>+$141.81K</t>
         </is>
       </c>
-      <c r="G67" s="6" t="inlineStr">
+      <c r="G69" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H67" s="6" t="inlineStr">
+      <c r="H69" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="6" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B68" s="5" t="n">
+      <c r="B70" s="2" t="n">
         <v>29651.1</v>
       </c>
-      <c r="C68" s="5" t="n">
+      <c r="C70" s="2" t="n">
         <v>29630</v>
       </c>
-      <c r="D68" s="6" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E68" s="8" t="inlineStr">
+      <c r="E70" s="8" t="inlineStr">
         <is>
           <t>+$57.91K</t>
         </is>
       </c>
-      <c r="F68" s="6" t="inlineStr">
+      <c r="F70" s="3" t="inlineStr">
         <is>
           <t>+$124.09K</t>
         </is>
       </c>
-      <c r="G68" s="6" t="inlineStr">
+      <c r="G70" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H68" s="6" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B69" s="5" t="n">
-        <v>94.08</v>
-      </c>
-      <c r="C69" s="5" t="n">
-        <v>146</v>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E69" s="8" t="inlineStr">
-        <is>
-          <t>+$55.63K</t>
-        </is>
-      </c>
-      <c r="F69" s="6" t="inlineStr">
-        <is>
-          <t>+$113.65K</t>
-        </is>
-      </c>
-      <c r="G69" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H69" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B70" s="5" t="n">
-        <v>29611.1</v>
-      </c>
-      <c r="C70" s="5" t="n">
-        <v>29590</v>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E70" s="8" t="inlineStr">
-        <is>
-          <t>+$97.50K</t>
-        </is>
-      </c>
-      <c r="F70" s="6" t="inlineStr">
-        <is>
-          <t>+$106.36K</t>
-        </is>
-      </c>
-      <c r="G70" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H70" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+      <c r="H70" s="3" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>94.08</v>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>+$55.63K</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>+$113.65K</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B71" s="2" t="n">
-        <v>29446.1</v>
-      </c>
-      <c r="C71" s="2" t="n">
-        <v>29425</v>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="B72" s="2" t="n">
+        <v>29611.1</v>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>29590</v>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E71" s="9" t="inlineStr">
-        <is>
-          <t>+$78.59K</t>
-        </is>
-      </c>
-      <c r="F71" s="3" t="inlineStr">
-        <is>
-          <t>+$95.13K</t>
-        </is>
-      </c>
-      <c r="G71" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H71" s="3" t="inlineStr">
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>+$97.50K</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>+$106.36K</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B72" s="5" t="n">
-        <v>29381.1</v>
-      </c>
-      <c r="C72" s="5" t="n">
-        <v>29360</v>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E72" s="8" t="inlineStr">
-        <is>
-          <t>+$67.36K</t>
-        </is>
-      </c>
-      <c r="F72" s="6" t="inlineStr">
-        <is>
-          <t>+$88.63K</t>
-        </is>
-      </c>
-      <c r="G72" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H72" s="6" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
@@ -5928,225 +5982,297 @@
         </is>
       </c>
       <c r="B73" s="5" t="n">
+        <v>29446.1</v>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>29425</v>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E73" s="9" t="inlineStr">
+        <is>
+          <t>+$78.59K</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>+$95.13K</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>29381.1</v>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>29360</v>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>+$67.36K</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>+$88.63K</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n">
         <v>29391.1</v>
       </c>
-      <c r="C73" s="5" t="n">
+      <c r="C75" s="2" t="n">
         <v>29370</v>
       </c>
-      <c r="D73" s="6" t="inlineStr">
+      <c r="D75" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E73" s="8" t="inlineStr">
+      <c r="E75" s="8" t="inlineStr">
         <is>
           <t>+$78.00K</t>
         </is>
       </c>
-      <c r="F73" s="6" t="inlineStr">
+      <c r="F75" s="3" t="inlineStr">
         <is>
           <t>+$78.00K</t>
         </is>
       </c>
-      <c r="G73" s="6" t="inlineStr">
+      <c r="G75" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H73" s="6" t="inlineStr">
+      <c r="H75" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="6" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B74" s="5" t="n">
+      <c r="B76" s="2" t="n">
         <v>29721.1</v>
       </c>
-      <c r="C74" s="5" t="n">
+      <c r="C76" s="2" t="n">
         <v>29700</v>
       </c>
-      <c r="D74" s="6" t="inlineStr">
+      <c r="D76" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E74" s="8" t="inlineStr">
+      <c r="E76" s="8" t="inlineStr">
         <is>
           <t>+$46.09K</t>
         </is>
       </c>
-      <c r="F74" s="6" t="inlineStr">
+      <c r="F76" s="3" t="inlineStr">
         <is>
           <t>+$67.36K</t>
         </is>
       </c>
-      <c r="G74" s="6" t="inlineStr">
+      <c r="G76" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H74" s="6" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="6" t="inlineStr">
+      <c r="H76" s="3" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="B75" s="5" t="n">
+      <c r="B77" s="2" t="n">
         <v>84.42</v>
       </c>
-      <c r="C75" s="5" t="n">
+      <c r="C77" s="2" t="n">
         <v>131</v>
       </c>
-      <c r="D75" s="6" t="inlineStr">
+      <c r="D77" s="3" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="E75" s="7" t="inlineStr">
+      <c r="E77" s="4" t="inlineStr">
         <is>
           <t>-$18.65K</t>
         </is>
       </c>
-      <c r="F75" s="6" t="inlineStr">
+      <c r="F77" s="3" t="inlineStr">
         <is>
           <t>+$34.94K</t>
         </is>
       </c>
-      <c r="G75" s="6" t="inlineStr">
+      <c r="G77" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H75" s="6" t="inlineStr">
+      <c r="H77" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="6" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="B76" s="5" t="n">
+      <c r="B78" s="2" t="n">
         <v>101.17</v>
       </c>
-      <c r="C76" s="5" t="n">
+      <c r="C78" s="2" t="n">
         <v>157</v>
       </c>
-      <c r="D76" s="6" t="inlineStr">
+      <c r="D78" s="3" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="E76" s="8" t="inlineStr">
+      <c r="E78" s="8" t="inlineStr">
         <is>
           <t>+$3.55K</t>
         </is>
       </c>
-      <c r="F76" s="6" t="inlineStr">
+      <c r="F78" s="3" t="inlineStr">
         <is>
           <t>+$3.55K</t>
         </is>
       </c>
-      <c r="G76" s="6" t="inlineStr">
+      <c r="G78" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H76" s="6" t="inlineStr">
+      <c r="H78" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="6" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="B77" s="5" t="n">
+      <c r="B79" s="2" t="n">
         <v>99.23999999999999</v>
       </c>
-      <c r="C77" s="5" t="n">
+      <c r="C79" s="2" t="n">
         <v>154</v>
       </c>
-      <c r="D77" s="6" t="inlineStr">
+      <c r="D79" s="3" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="E77" s="8" t="inlineStr">
+      <c r="E79" s="8" t="inlineStr">
         <is>
           <t>+$3.06K</t>
         </is>
       </c>
-      <c r="F77" s="6" t="inlineStr">
+      <c r="F79" s="3" t="inlineStr">
         <is>
           <t>+$3.06K</t>
         </is>
       </c>
-      <c r="G77" s="6" t="inlineStr">
+      <c r="G79" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H77" s="6" t="inlineStr">
+      <c r="H79" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="6" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="B78" s="5" t="n">
+      <c r="B80" s="2" t="n">
         <v>102.46</v>
       </c>
-      <c r="C78" s="5" t="n">
+      <c r="C80" s="2" t="n">
         <v>159</v>
       </c>
-      <c r="D78" s="6" t="inlineStr">
+      <c r="D80" s="3" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="E78" s="8" t="inlineStr">
+      <c r="E80" s="8" t="inlineStr">
         <is>
           <t>+$307</t>
         </is>
       </c>
-      <c r="F78" s="6" t="inlineStr">
+      <c r="F80" s="3" t="inlineStr">
         <is>
           <t>+$307</t>
         </is>
       </c>
-      <c r="G78" s="6" t="inlineStr">
+      <c r="G80" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H78" s="6" t="inlineStr">
+      <c r="H80" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H78"/>
+  <autoFilter ref="A1:H80"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>